--- a/output/pdf_financials_xlsx/GLO.xlsx
+++ b/output/pdf_financials_xlsx/GLO.xlsx
@@ -7436,25 +7436,25 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.017961</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-6.001173</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-2.651179</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-9.604590999999999</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.407627</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.241167</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>1.669276</v>
+        <v>1.386432</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>0</v>
@@ -34402,7 +34402,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -36301,7 +36305,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -39748,7 +39756,11 @@
           <t>Advance payments for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -39952,7 +39964,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -41795,7 +41811,11 @@
           <t>Exploration and evaluation expenditures 9</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GLO.xlsx
+++ b/output/pdf_financials_xlsx/GLO.xlsx
@@ -2512,7 +2512,7 @@
         <v>3.890665</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>34.179449</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>8.400008</v>
@@ -2521,10 +2521,10 @@
         <v>24.857915</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>18.673229</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>13.117054</v>
       </c>
     </row>
     <row r="35">
@@ -2628,7 +2628,7 @@
         <v>3.890665</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>34.179449</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>8.400008</v>
@@ -2637,10 +2637,10 @@
         <v>24.857915</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>18.673229</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>13.117054</v>
       </c>
     </row>
     <row r="37">
@@ -3324,7 +3324,7 @@
         <v>0.03431</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>34.526643</v>
+        <v>0.347194</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.131009</v>
@@ -3333,10 +3333,10 @@
         <v>0.2077</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>18.725767</v>
+        <v>0.052538</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>13.183243</v>
+        <v>0.066189</v>
       </c>
     </row>
     <row r="49">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -58885,7 +58885,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -58978,7 +58978,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -59683,7 +59683,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -59780,7 +59780,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -64287,7 +64287,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
@@ -64380,7 +64380,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">

--- a/output/pdf_financials_xlsx/GLO.xlsx
+++ b/output/pdf_financials_xlsx/GLO.xlsx
@@ -2839,16 +2839,16 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.003995</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.014279</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.07018000000000001</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.269694</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -2897,16 +2897,16 @@
         <v>0.09574100000000001</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.11061</v>
+        <v>0.114605</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.101838</v>
+        <v>0.116117</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.118142</v>
+        <v>0.188322</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.428317</v>
+        <v>0.698011</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.31997</v>
@@ -3303,16 +3303,16 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.024732</v>
+        <v>0.020737</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.017908</v>
+        <v>0.003629</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.020775</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.019851</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.028214</v>
@@ -3789,16 +3789,16 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.036877</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.026192</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.029031</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>0.029031</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.019417</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.020128</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.025587</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.028593</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0</v>
@@ -4294,10 +4294,10 @@
         <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.594798</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>3.082915</v>
       </c>
       <c r="P64" s="3" t="n">
         <v>0</v>
@@ -4447,40 +4447,40 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.06796000000000001</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.057133</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.051729</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.0439</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>1.986733</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>3.368355</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>5.553863</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>10.175429</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>16.491264</v>
       </c>
     </row>
     <row r="68">
@@ -6771,55 +6771,55 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.032261</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.150078</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.377193</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.080067</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.313954</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>0.055179</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.367264</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.011952</v>
       </c>
       <c r="J107" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>1.681692</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>1.019279</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>2.866444</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>4.322289</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>3.800164</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>2.200205</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>0.683914</v>
       </c>
     </row>
     <row r="108">
@@ -6948,10 +6948,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.237801</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.291097</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007969</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.471121</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.353469</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>-0.370121</v>
@@ -7329,13 +7329,13 @@
         <v>0</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-0.214299</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.233191</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.084814</v>
       </c>
       <c r="Q116" s="3" t="n">
         <v>0</v>
@@ -7598,16 +7598,16 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.19443</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-0.9825970000000001</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-0.03474</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.00284</v>
       </c>
       <c r="K121" s="3" t="n">
         <v>0</v>
@@ -8371,13 +8371,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007969</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.471121</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.353469</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>-0.370121</v>
@@ -8429,13 +8429,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.393239</v>
+        <v>-1.401208</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.665156</v>
+        <v>-2.136277</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.364183</v>
+        <v>0.010714</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>0.576829</v>
@@ -32433,7 +32433,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -32714,7 +32718,11 @@
           <t>Stock option expense 16</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -35317,7 +35325,11 @@
           <t>Stock option expense 17</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -36208,7 +36220,11 @@
           <t>Purchase intangible assets</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -42401,7 +42417,11 @@
           <t>Share repurchase 15</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -42601,7 +42621,11 @@
           <t>Stock option expense 12</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -42900,7 +42924,11 @@
           <t>Share repurchase 11</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -44886,7 +44914,11 @@
           <t>Stock option expense 13</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -45286,7 +45318,11 @@
           <t>Stock option expense</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E373" s="5" t="n">
         <v>0.032261</v>
       </c>
@@ -47577,7 +47613,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E396" s="5" t="n">
         <v>1.491782</v>
       </c>
@@ -48882,7 +48922,11 @@
           <t>Acquisition of equipment 8</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -49084,7 +49128,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -49282,7 +49330,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -52001,7 +52053,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E440" s="5" t="n">
         <v>-0.902755</v>
       </c>
@@ -53928,7 +53984,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E459" s="5" t="n">
         <v>-0.007969</v>
       </c>
